--- a/AAII_Financials/Quarterly/SHKLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SHKLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>SHKLY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -669,55 +669,70 @@
     <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +766,20 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,8 +813,20 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +860,20 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +887,12 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +926,20 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +973,20 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +1020,20 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +1067,20 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,8 +1091,12 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1023,8 +1130,20 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1058,8 +1177,20 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1204,12 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1108,8 +1243,20 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1143,8 +1290,20 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,8 +1337,20 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1213,8 +1384,20 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1248,8 +1431,20 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,8 +1478,20 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1318,8 +1525,20 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1353,8 +1572,20 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1619,20 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1666,20 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1713,20 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1760,20 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1528,8 +1807,20 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1563,8 +1854,20 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,8 +1901,20 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1633,48 +1948,72 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +2027,12 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,323 +2046,435 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2632300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2586200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1209100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1193700</v>
+      </c>
+      <c r="H41" s="3">
         <v>1638000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>1704400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>2163700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>2177600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>2150900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>2090200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>1560600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>1647600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>2220700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>2152900</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3293200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3235500</v>
+      </c>
+      <c r="F42" s="3">
+        <v>4943800</v>
+      </c>
+      <c r="G42" s="3">
+        <v>4880600</v>
+      </c>
+      <c r="H42" s="3">
         <v>3992800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>4154800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>4685700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>4715800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>4731200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>4597800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>4488100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>4738400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>4184400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>4056700</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4535700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4456200</v>
+      </c>
+      <c r="F43" s="3">
+        <v>4372200</v>
+      </c>
+      <c r="G43" s="3">
+        <v>4316400</v>
+      </c>
+      <c r="H43" s="3">
         <v>3739700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>3891400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>3396800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>3418600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>2408500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>2340600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>2143300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>2262800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>2353100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>2281300</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3178700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3123000</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1657000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1635800</v>
+      </c>
+      <c r="H44" s="3">
         <v>1594700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>1659400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>1815700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>1827400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>1881100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>1828000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>1992800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>2104000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>1957600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>1897900</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>373100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>366600</v>
+      </c>
+      <c r="F45" s="3">
+        <v>298500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>294700</v>
+      </c>
+      <c r="H45" s="3">
         <v>481300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>500800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>310000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>312000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>411300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>399700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>252800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>266900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>215600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>209000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14872500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>14611800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>13301900</v>
+      </c>
+      <c r="G46" s="3">
+        <v>13132000</v>
+      </c>
+      <c r="H46" s="3">
         <v>12388800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>12891500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>12998100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>13081600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>12278700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>11932500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>11056300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>11672900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>11591800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>11238100</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2686700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2639600</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2455700</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2424300</v>
+      </c>
+      <c r="H47" s="3">
         <v>1636900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="I47" s="3">
         <v>1703300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>210100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>211500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>1104700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>1073500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>278400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>294000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>284300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2392600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2350700</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2436500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2405300</v>
+      </c>
+      <c r="H48" s="3">
         <v>2422100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>2520300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>2467500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>2483400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>2550200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>2478300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>2444600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>2580900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>2583600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>2504700</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F49" s="3">
+        <v>27800</v>
+      </c>
+      <c r="G49" s="3">
         <v>27500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
+        <v>27500</v>
+      </c>
+      <c r="I49" s="3">
         <v>28600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>28400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>28600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>31200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>30300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>36800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>38900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>43700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2508,20 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2555,67 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>106800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>116900</v>
+      </c>
+      <c r="G52" s="3">
+        <v>115400</v>
+      </c>
+      <c r="H52" s="3">
         <v>183000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>190500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>1391900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>1400900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>177300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>172300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>682100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>720100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>149800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>145200</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2649,67 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21893000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21509200</v>
+      </c>
+      <c r="F54" s="3">
+        <v>19577000</v>
+      </c>
+      <c r="G54" s="3">
+        <v>19326900</v>
+      </c>
+      <c r="H54" s="3">
         <v>17779900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>18501300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>18266400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>18383700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>17174900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>16690700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>15485300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>16348900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>15316700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>14849300</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2723,12 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,218 +2742,294 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10000500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9825200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>8435100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>8327300</v>
+      </c>
+      <c r="H57" s="3">
         <v>7271000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>7566000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>7178400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>7224500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>6575200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>6389800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>5462600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>5767300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>4823900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>4676600</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>705600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>693200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>869000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>857900</v>
+      </c>
+      <c r="H58" s="3">
         <v>717300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>746400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>1014400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>1020900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>692300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>672800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>582500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>615000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>564600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>547400</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2259700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1935200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1910500</v>
+      </c>
+      <c r="H59" s="3">
         <v>1983700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>2064200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>2363300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>2378400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>2124600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>2064700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>2409800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>2544200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>2728800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>2645500</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14046600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>13800400</v>
+      </c>
+      <c r="F60" s="3">
+        <v>12198200</v>
+      </c>
+      <c r="G60" s="3">
+        <v>12042400</v>
+      </c>
+      <c r="H60" s="3">
         <v>10830700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>11270200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>11461500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>11535200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>10228600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>9940300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>9151900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>9662300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>8904300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>8632600</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>76300</v>
+      </c>
+      <c r="F61" s="3">
+        <v>60900</v>
+      </c>
+      <c r="G61" s="3">
+        <v>60100</v>
+      </c>
+      <c r="H61" s="3">
         <v>64300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>66900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>31000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>31200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>20100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>19600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>2900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>53200</v>
+      </c>
+      <c r="F62" s="3">
+        <v>59200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>58500</v>
+      </c>
+      <c r="H62" s="3">
         <v>61700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>64200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>54900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>55200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>57900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>56200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>72400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>76400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>76200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>73900</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +3063,20 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +3110,20 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +3157,67 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14285000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14034500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>12419800</v>
+      </c>
+      <c r="G66" s="3">
+        <v>12261100</v>
+      </c>
+      <c r="H66" s="3">
         <v>11045800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>11494000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>11647900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>11722700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>10411200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>10117700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>9319500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>9839200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>9077600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>8800600</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +3231,12 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +3270,20 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +3317,20 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +3364,20 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +3411,67 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4307600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4232100</v>
+      </c>
+      <c r="F72" s="3">
+        <v>3965800</v>
+      </c>
+      <c r="G72" s="3">
+        <v>3915100</v>
+      </c>
+      <c r="H72" s="3">
         <v>3615100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>3761800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>3528700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>3551400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>3527600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>3428200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>3060000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>3230600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>2973400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>2882700</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +3505,20 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3552,20 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3599,67 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6432300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6319600</v>
+      </c>
+      <c r="F76" s="3">
+        <v>6033400</v>
+      </c>
+      <c r="G76" s="3">
+        <v>5956300</v>
+      </c>
+      <c r="H76" s="3">
         <v>5639100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>5867900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>5558300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>5594000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>5679400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>5519300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>5165200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>5453200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>5210000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>5051000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,48 +3693,72 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3013,8 +3792,20 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,43 +3819,59 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>58900</v>
+      </c>
+      <c r="G83" s="3">
+        <v>59300</v>
+      </c>
+      <c r="H83" s="3">
         <v>48400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>47100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>54000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>57000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>49600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>48100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>52100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>55100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>54900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3905,20 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3952,20 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3999,20 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +4046,20 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +4093,67 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>283500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>278500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>255200</v>
+      </c>
+      <c r="G89" s="3">
+        <v>252000</v>
+      </c>
+      <c r="H89" s="3">
         <v>325400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>338600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>367200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>369500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>588700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>572100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>208200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>219800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>677000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>656300</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +4167,59 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-84600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-96300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-100200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-57200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-57500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-88700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-86200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-88900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-93900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-29800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-28900</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +4253,20 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +4300,67 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>653200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>641800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-482500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-476300</v>
+      </c>
+      <c r="H94" s="3">
         <v>-282900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-294400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>-311800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>-313800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-275700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-267900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-492900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-520400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-923700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-895500</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,43 +4374,59 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>234300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>230200</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>307200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="I96" s="3">
         <v>319700</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>57300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="M96" s="3">
         <v>55700</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>112800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="Q96" s="3">
         <v>109400</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +4460,20 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +4507,20 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,109 +4554,157 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-237900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-233700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="H100" s="3">
         <v>-298000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-310100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-29500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-29700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-48000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-46700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>14500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>15300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-115200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-111700</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F101" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G101" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="J101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
         <v>6400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>-2100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>-2100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="N101" s="3">
         <v>11800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>12400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="P101" s="3">
         <v>-2900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>684800</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-229900</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-227000</v>
+      </c>
+      <c r="H102" s="3">
         <v>-258100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-268600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>32500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>32700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>265600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>258100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-264200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-278900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-364100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>-353000</v>
       </c>
     </row>
